--- a/src/src/main/webapp/portal/asset/contract/contractImport/APM_Contract_Service_Template.xlsx
+++ b/src/src/main/webapp/portal/asset/contract/contractImport/APM_Contract_Service_Template.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{F5905874-1FB9-4CC8-8ED1-106356BA452A}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{358267FF-01A9-4FDE-A5E7-0ADD1DC1CB4F}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Contract Service List" sheetId="1" r:id="rId1"/>
+    <sheet name="Contract List" sheetId="1" r:id="rId1"/>
+    <sheet name="填写说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -46,11 +47,41 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>结束月数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>供应商</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>填写说明</t>
+  </si>
+  <si>
+    <t>1. 合同名称必须填写</t>
+  </si>
+  <si>
+    <t>2. 开始时间必填</t>
+  </si>
+  <si>
+    <t>3. 结束时间 =  开始时间+ X 合同时间（月）-1； 举例， 合同开始日期 2018-1-1， 为期一个月，结束时间= 2018-1-31</t>
+  </si>
+  <si>
+    <t>4. 结束时间和合同时间（月）两者必须填一个，两者都有内容的情况下， 优先结束时间。</t>
+  </si>
+  <si>
+    <t>5. 供应商可不填， 输入值必须填系统已经存在的供应商，否则导入失败</t>
+  </si>
+  <si>
+    <t>合同时间(月)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试合同</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test123456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试供应商</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -62,7 +93,7 @@
     <numFmt numFmtId="176" formatCode="&quot;¥&quot;#,##0.00;[Red]&quot;¥&quot;#,##0.00"/>
     <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,16 +108,36 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -94,16 +145,89 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -384,42 +508,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9" style="4"/>
-    <col min="2" max="3" width="10.5" style="4" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9" style="2"/>
-    <col min="7" max="7" width="9" style="3"/>
-    <col min="8" max="8" width="9" style="4"/>
+    <col min="1" max="1" width="13.375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="20.75" style="4" customWidth="1"/>
+    <col min="3" max="3" width="20.125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="17.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="3" customWidth="1"/>
+    <col min="8" max="8" width="26.375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="G1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1">
+        <v>666</v>
+      </c>
+      <c r="E2" s="2">
+        <v>43282</v>
+      </c>
+      <c r="F2" s="2">
+        <v>43311</v>
       </c>
     </row>
   </sheetData>
@@ -427,4 +572,132 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0115A0BF-3840-42DC-AEF5-75142607EF1A}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="7" max="7" width="53.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="8"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="8"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="8"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="8"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="5"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="8"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="5"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="8"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="5"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="8"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="5"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A9:G9"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/src/main/webapp/portal/asset/contract/contractImport/APM_Contract_Service_Template.xlsx
+++ b/src/src/main/webapp/portal/asset/contract/contractImport/APM_Contract_Service_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{358267FF-01A9-4FDE-A5E7-0ADD1DC1CB4F}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{FEF8736F-5297-461C-970D-2A6F594C882A}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,9 +63,6 @@
     <t>3. 结束时间 =  开始时间+ X 合同时间（月）-1； 举例， 合同开始日期 2018-1-1， 为期一个月，结束时间= 2018-1-31</t>
   </si>
   <si>
-    <t>4. 结束时间和合同时间（月）两者必须填一个，两者都有内容的情况下， 优先结束时间。</t>
-  </si>
-  <si>
     <t>5. 供应商可不填， 输入值必须填系统已经存在的供应商，否则导入失败</t>
   </si>
   <si>
@@ -82,6 +79,10 @@
   </si>
   <si>
     <t>测试供应商</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. 结束时间和合同时间(月)两者必须填一个，两者都有内容的情况下， 优先结合同时间(月)，如果有确切的结束时间，合同时间(月)不要填写。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -212,10 +213,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -521,41 +522,41 @@
     <col min="8" max="8" width="26.375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="6" t="s">
+      <c r="G1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="D2" s="1">
         <v>666</v>
@@ -579,7 +580,7 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="7" max="7" width="53.375" customWidth="1"/>
+    <col min="7" max="7" width="76.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
@@ -594,7 +595,7 @@
       <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="7"/>
@@ -605,7 +606,7 @@
       <c r="G2" s="8"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
@@ -616,7 +617,7 @@
       <c r="G3" s="8"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="7"/>
@@ -627,8 +628,8 @@
       <c r="G4" s="8"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>11</v>
+      <c r="A5" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -638,8 +639,8 @@
       <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>12</v>
+      <c r="A6" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -649,7 +650,7 @@
       <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="5"/>
+      <c r="A7" s="6"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -658,7 +659,7 @@
       <c r="G7" s="8"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="5"/>
+      <c r="A8" s="6"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -667,7 +668,7 @@
       <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5"/>
+      <c r="A9" s="6"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -676,7 +677,7 @@
       <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="5"/>
+      <c r="A10" s="6"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -699,5 +700,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/src/main/webapp/portal/asset/contract/contractImport/APM_Contract_Service_Template.xlsx
+++ b/src/src/main/webapp/portal/asset/contract/contractImport/APM_Contract_Service_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{FEF8736F-5297-461C-970D-2A6F594C882A}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{3DB82518-F234-476F-9E77-0DAA0F4FE54F}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -83,6 +83,14 @@
   </si>
   <si>
     <t>4. 结束时间和合同时间(月)两者必须填一个，两者都有内容的情况下， 优先结合同时间(月)，如果有确切的结束时间，合同时间(月)不要填写。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外贸合同号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发票号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -509,20 +517,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="20.75" style="4" customWidth="1"/>
-    <col min="3" max="3" width="20.125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="17.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.5" style="3" customWidth="1"/>
-    <col min="8" max="8" width="26.375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="15.625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="4" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="20.125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="25.375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -530,41 +540,47 @@
         <v>3</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1">
+      <c r="F2" s="1">
         <v>666</v>
       </c>
-      <c r="E2" s="2">
+      <c r="G2" s="2">
         <v>43282</v>
       </c>
-      <c r="F2" s="2">
+      <c r="H2" s="2">
         <v>43311</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/asset/contract/contractImport/APM_Contract_Service_Template.xlsx
+++ b/src/src/main/webapp/portal/asset/contract/contractImport/APM_Contract_Service_Template.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="19126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{3DB82518-F234-476F-9E77-0DAA0F4FE54F}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366FAF5D-4720-4048-8CCA-6A7CEA127914}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -91,6 +91,14 @@
   </si>
   <si>
     <t>发票号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>报告号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test123456</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -517,22 +525,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="12.375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="4" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="20.125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="25.375" style="4" customWidth="1"/>
+    <col min="2" max="3" width="12.375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="13.25" style="4" customWidth="1"/>
+    <col min="5" max="5" width="13.625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="20.125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="11.375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="25.375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -540,47 +548,53 @@
         <v>3</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>666</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2">
         <v>43282</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>43311</v>
       </c>
     </row>
